--- a/outputs/daily/hr_rankings_2026-07-18.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-18.xlsx
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>65.09999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1651,7 +1651,7 @@
         <v>67.2</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -1661,39 +1661,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -2164,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2748,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>59.4</v>
+        <v>60</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2762,7 +2758,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2775,7 +2771,7 @@
         <v>67.2</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
@@ -2785,39 +2781,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -2983,27 +2975,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>671277</t>
+          <t>693307</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Luis García Jr.</t>
+          <t>Dillon Dingler</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-19T02:05:00Z</t>
+          <t>2026-07-19T02:07:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3018,12 +3010,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>J.T. Ginn</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>669372</t>
+          <t>680570</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -3032,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>59.3</v>
+        <v>59.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3046,26 +3038,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>48.7</v>
+        <v>49.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>33.3</v>
+        <v>60.5</v>
       </c>
       <c r="R10" t="n">
-        <v>71.40000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="S10" t="n">
         <v>100</v>
       </c>
       <c r="T10" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>66.90000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3100,7 +3092,7 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -3117,27 +3109,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/23, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 14.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3147,112 +3139,112 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.81</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>46.57</t>
+          <t>46.33</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>91.39</t>
+          <t>89.79</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.8855</t>
+          <t>101.1126</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4987</t>
+          <t>0.5072</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.2072</t>
+          <t>0.2193</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3537</t>
+          <t>0.3685</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>73.24</t>
+          <t>71.91</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>34.44</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.66</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>0.2149</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>37.57</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>87.56</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.3775</t>
+          <t>0.531</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1428</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr"/>
@@ -3263,12 +3255,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>693307</t>
+          <t>690993</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dillon Dingler</t>
+          <t>Colt Keith</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3293,7 +3285,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3312,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>59.1</v>
+        <v>59.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3326,11 +3318,11 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>49.3</v>
+        <v>37.5</v>
       </c>
       <c r="Q11" t="n">
         <v>60.5</v>
@@ -3339,49 +3331,45 @@
         <v>67.2</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>8.1</v>
+        <v>38.7</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -3401,27 +3389,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/23, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3431,67 +3419,67 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>8.36</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>42.72</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.79</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>101.1126</t>
+          <t>100.2207</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.5072</t>
+          <t>0.4342</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.2193</t>
+          <t>0.1716</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3685</t>
+          <t>0.3284</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>71.91</t>
+          <t>71.61</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>40.66</t>
+          <t>38.78</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.2149</t>
+          <t>0.1493</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -3547,27 +3535,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>690993</t>
+          <t>671277</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Colt Keith</t>
+          <t>Luis García Jr.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-19T02:07:00Z</t>
+          <t>2026-07-19T02:05:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3577,17 +3565,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>J.T. Ginn</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>680570</t>
+          <t>669372</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3596,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>59</v>
+        <v>59.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3610,65 +3598,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>37.5</v>
+        <v>48.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>60.5</v>
+        <v>33.3</v>
       </c>
       <c r="R12" t="n">
-        <v>67.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>38.7</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3685,19 +3669,19 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AK12" t="inlineStr">
         <is>
           <t>Hot streak: 2 HR in last 7 games</t>
@@ -3705,7 +3689,7 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 14.2 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3715,112 +3699,112 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>42.72</t>
+          <t>46.57</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>91.39</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100.2207</t>
+          <t>101.8855</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4342</t>
+          <t>0.4987</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1716</t>
+          <t>0.2072</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3284</t>
+          <t>0.3537</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>71.61</t>
+          <t>73.24</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>34.44</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>38.78</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1493</t>
+          <t>0.237</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>37.57</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>87.56</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>0.3775</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.1428</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr"/>
@@ -3880,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>58.7</v>
+        <v>59.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3894,7 +3878,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3907,7 +3891,7 @@
         <v>67.2</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
@@ -3917,39 +3901,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4115,27 +4095,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>646240</t>
+          <t>805808</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rafael Devers</t>
+          <t>Kevin McGonigle</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-19T00:08:00Z</t>
+          <t>2026-07-19T02:07:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4145,17 +4125,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>680570</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4164,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>57.4</v>
+        <v>57.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4178,26 +4158,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>58.7</v>
+        <v>34.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.4</v>
+        <v>60.5</v>
       </c>
       <c r="R14" t="n">
-        <v>38.4</v>
+        <v>67.2</v>
       </c>
       <c r="S14" t="n">
-        <v>94.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T14" t="n">
         <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>36.3</v>
+        <v>33.7</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -4211,7 +4191,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -4232,7 +4212,7 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -4254,7 +4234,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -4264,127 +4244,127 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Last 7 games: 6/27, 1 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 14.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>51.97</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>103.1178</t>
+          <t>98.4601</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.4653</t>
+          <t>0.441</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.2301</t>
+          <t>0.173</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3376</t>
+          <t>0.363</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>71.74</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>42.71</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>89.45</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3835</t>
+          <t>0.531</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1513</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>29.11</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -4395,24 +4375,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>686527</t>
+          <t>646240</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dominic Canzone</t>
+          <t>Rafael Devers</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-07-19T00:08:00Z</t>
@@ -4420,22 +4400,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Logan Webb</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>657277</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4444,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4462,22 +4442,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>62.8</v>
+        <v>58.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>31.2</v>
+        <v>41.4</v>
       </c>
       <c r="R15" t="n">
         <v>38.4</v>
       </c>
       <c r="S15" t="n">
-        <v>96.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T15" t="n">
         <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>49.7</v>
+        <v>36.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -4491,7 +4471,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -4534,22 +4514,22 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 9.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 14.8 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4559,97 +4539,97 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>12.92</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>51.97</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>92.58</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>103.1752</t>
+          <t>103.1178</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.5218</t>
+          <t>0.4653</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.2437</t>
+          <t>0.2301</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3718</t>
+          <t>0.3376</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>74.29</t>
+          <t>71.74</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>44.61</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>0.227</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>40.69</t>
+          <t>42.71</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>89.21</t>
+          <t>89.45</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3835</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1289</t>
+          <t>0.1513</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>29.11</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
@@ -4675,47 +4655,47 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>805808</t>
+          <t>686527</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kevin McGonigle</t>
+          <t>Dominic Canzone</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-19T02:07:00Z</t>
+          <t>2026-07-19T00:08:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>Logan Webb</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>680570</t>
+          <t>657277</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4724,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>57.1</v>
+        <v>57.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4738,65 +4718,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>34.1</v>
+        <v>62.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>60.5</v>
+        <v>31.2</v>
       </c>
       <c r="R16" t="n">
-        <v>67.2</v>
+        <v>38.4</v>
       </c>
       <c r="S16" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T16" t="n">
         <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>33.7</v>
+        <v>49.7</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4818,137 +4794,137 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 9.8 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>48.51</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>92.58</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>98.4601</t>
+          <t>103.1752</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.441</t>
+          <t>0.5218</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.2437</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>0.3718</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>74.29</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>44.61</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.237</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>40.69</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>89.21</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.1289</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr"/>
@@ -6104,7 +6080,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6384,7 +6360,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -8344,7 +8320,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -8599,27 +8575,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>695734</t>
+          <t>663837</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Daylen Lile</t>
+          <t>Matt Vierling</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-19T02:05:00Z</t>
+          <t>2026-07-19T02:07:00Z</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8629,17 +8605,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>J.T. Ginn</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>669372</t>
+          <t>680570</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -8648,7 +8624,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>47.7</v>
+        <v>47.9</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -8662,26 +8638,26 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>30.5</v>
+        <v>30.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>33.3</v>
+        <v>60.5</v>
       </c>
       <c r="R30" t="n">
-        <v>71.40000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="S30" t="n">
-        <v>76.2</v>
+        <v>52.4</v>
       </c>
       <c r="T30" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U30" t="n">
-        <v>21.8</v>
+        <v>25.8</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -8695,7 +8671,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -8716,7 +8692,7 @@
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr"/>
@@ -8733,27 +8709,27 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/28, 1 HR</t>
+          <t>Last 7 games: 7/24, 0 HR</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 14.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -8763,112 +8739,112 @@
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>36.74</t>
+          <t>38.71</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>88.34</t>
+          <t>89.05</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>98.6898</t>
+          <t>99.1028</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.3947</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1419</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>0.3256</t>
+          <t>0.3128</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>70.32</t>
+          <t>71.07</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>41.01</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>31.78</t>
+          <t>31.97</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>0.1717</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>37.57</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>87.56</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>0.3775</t>
+          <t>0.531</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
-          <t>0.1428</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr"/>
@@ -8879,27 +8855,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>663728</t>
+          <t>695734</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cal Raleigh</t>
+          <t>Daylen Lile</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-19T00:08:00Z</t>
+          <t>2026-07-19T02:05:00Z</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -8914,12 +8890,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Logan Webb</t>
+          <t>J.T. Ginn</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>657277</t>
+          <t>669372</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -8928,7 +8904,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -8942,26 +8918,26 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>50.2</v>
+        <v>30.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>30.2</v>
+        <v>33.3</v>
       </c>
       <c r="R31" t="n">
-        <v>38.4</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="S31" t="n">
         <v>76.2</v>
       </c>
       <c r="T31" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U31" t="n">
-        <v>12</v>
+        <v>21.8</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -9013,142 +8989,142 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 4/28, 1 HR</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.2% barrel, 9.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 14.2 HR allowed</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>36.74</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>89.06</t>
+          <t>88.34</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>100.0801</t>
+          <t>98.6898</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>0.4105</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>0.2173</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>0.3122</t>
+          <t>0.3256</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>74.92</t>
+          <t>70.32</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>52.11</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>52.47</t>
+          <t>41.01</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>43.76</t>
+          <t>31.78</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.1999</t>
+          <t>0.1717</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>40.69</t>
+          <t>37.57</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>89.21</t>
+          <t>87.56</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3775</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
-          <t>0.1289</t>
+          <t>0.1428</t>
         </is>
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr"/>
@@ -9159,56 +9135,56 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>642350</t>
+          <t>663728</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jose Siri</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-19T02:07:00Z</t>
+          <t>2026-07-19T00:08:00Z</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Logan Webb</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>669373</t>
+          <t>657277</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -9226,22 +9202,22 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>45</v>
+        <v>50.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>29.4</v>
+        <v>30.2</v>
       </c>
       <c r="R32" t="n">
-        <v>67.2</v>
+        <v>38.4</v>
       </c>
       <c r="S32" t="n">
-        <v>52.4</v>
+        <v>76.2</v>
       </c>
       <c r="T32" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U32" t="n">
-        <v>22.9</v>
+        <v>12</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -9255,7 +9231,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -9293,12 +9269,12 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -9308,12 +9284,12 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/11, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.5% barrel, 12.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.2% barrel, 9.8 HR allowed</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -9323,112 +9299,112 @@
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>37.63</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>86.51</t>
+          <t>89.06</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>99.085</t>
+          <t>100.0801</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4105</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>0.2022</t>
+          <t>0.2173</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>0.2862</t>
+          <t>0.3122</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>73.01</t>
+          <t>74.92</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>32.49</t>
+          <t>52.11</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>28.68</t>
+          <t>52.47</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>43.76</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.1635</t>
+          <t>0.1999</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>7.54</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>40.69</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>87.22</t>
+          <t>89.21</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>0.3538</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
-          <t>0.1268</t>
+          <t>0.1289</t>
         </is>
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr"/>
@@ -9439,24 +9415,24 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>663837</t>
+          <t>642350</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Matt Vierling</t>
+          <t>Jose Siri</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>2026-07-19T02:07:00Z</t>
@@ -9474,21 +9450,21 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>680570</t>
+          <t>669373</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>47.2</v>
+        <v>47.5</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -9502,65 +9478,61 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>30.7</v>
+        <v>45</v>
       </c>
       <c r="Q33" t="n">
-        <v>60.5</v>
+        <v>29.4</v>
       </c>
       <c r="R33" t="n">
         <v>67.2</v>
       </c>
       <c r="S33" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T33" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U33" t="n">
-        <v>25.8</v>
+        <v>22.9</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr"/>
@@ -9577,12 +9549,12 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -9592,112 +9564,112 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 0 HR</t>
+          <t>Last 7 games: 3/11, 0 HR</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.5% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>38.71</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>89.05</t>
+          <t>86.51</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>99.1028</t>
+          <t>99.085</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>0.3947</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>0.1419</t>
+          <t>0.2022</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>0.3128</t>
+          <t>0.2862</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>71.07</t>
+          <t>73.01</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>32.49</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>28.68</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>31.97</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.1635</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>87.22</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>0.3538</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.1268</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="BG33" t="inlineStr">
@@ -9723,27 +9695,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>668227</t>
+          <t>681546</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Randy Arozarena</t>
+          <t>James Outman</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-19T00:08:00Z</t>
+          <t>2026-07-19T02:07:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9753,17 +9725,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Logan Webb</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>657277</t>
+          <t>680570</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -9772,7 +9744,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>47</v>
+        <v>47.2</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -9786,26 +9758,26 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>40</v>
+        <v>27.7</v>
       </c>
       <c r="Q34" t="n">
-        <v>31.2</v>
+        <v>60.5</v>
       </c>
       <c r="R34" t="n">
-        <v>38.4</v>
+        <v>67.2</v>
       </c>
       <c r="S34" t="n">
-        <v>94.90000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T34" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U34" t="n">
-        <v>54.7</v>
+        <v>0.8</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -9819,7 +9791,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -9840,7 +9812,7 @@
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr"/>
@@ -9857,27 +9829,27 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 9.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -9887,112 +9859,112 @@
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>44.72</t>
+          <t>33.73</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>86.95</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>101.0066</t>
+          <t>98.0212</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>0.4226</t>
+          <t>0.2838</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.1697</t>
+          <t>0.1335</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.3438</t>
+          <t>0.2272</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>71.39</t>
+          <t>72.25</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>34.33</t>
+          <t>52.59</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>30.02</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.1754</t>
+          <t>0.1513</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>40.69</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>89.21</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.531</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>0.1289</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr"/>
@@ -10003,47 +9975,47 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>805779</t>
+          <t>668227</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jacob Wilson</t>
+          <t>Randy Arozarena</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-19T02:05:00Z</t>
+          <t>2026-07-19T00:08:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Zack Littell</t>
+          <t>Logan Webb</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>641793</t>
+          <t>657277</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -10066,26 +10038,26 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Good Environment, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.9</v>
+        <v>40</v>
       </c>
       <c r="Q35" t="n">
-        <v>67.7</v>
+        <v>31.2</v>
       </c>
       <c r="R35" t="n">
-        <v>71.40000000000001</v>
+        <v>38.4</v>
       </c>
       <c r="S35" t="n">
-        <v>93.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T35" t="n">
         <v>50</v>
       </c>
       <c r="U35" t="n">
-        <v>30</v>
+        <v>54.7</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -10099,7 +10071,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -10137,7 +10109,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
@@ -10147,132 +10119,132 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.9% barrel, 26.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 9.8 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>27.64</t>
+          <t>44.72</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>95.648</t>
+          <t>101.0066</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.3493</t>
+          <t>0.4226</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.0772</t>
+          <t>0.1697</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.2907</t>
+          <t>0.3438</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>64.04</t>
+          <t>71.39</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>24.69</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>32.46</t>
+          <t>34.33</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>19.76</t>
+          <t>22.14</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.1141</t>
+          <t>0.1754</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>44.12</t>
+          <t>40.69</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>91.39</t>
+          <t>89.21</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>0.5154</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>0.2341</t>
+          <t>0.1289</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -10283,27 +10255,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>670042</t>
+          <t>805779</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Luke Raley</t>
+          <t>Jacob Wilson</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-19T00:08:00Z</t>
+          <t>2026-07-19T02:05:00Z</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -10313,17 +10285,17 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Logan Webb</t>
+          <t>Zack Littell</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>657277</t>
+          <t>641793</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -10332,7 +10304,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>46.7</v>
+        <v>47</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -10346,26 +10318,26 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>54.2</v>
+        <v>2.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>31.2</v>
+        <v>67.7</v>
       </c>
       <c r="R36" t="n">
-        <v>38.4</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="S36" t="n">
-        <v>52.4</v>
+        <v>93.2</v>
       </c>
       <c r="T36" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U36" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -10379,7 +10351,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -10417,12 +10389,12 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -10432,127 +10404,127 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 9.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.9% barrel, 26.9 HR allowed</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>14.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>45.03</t>
+          <t>27.64</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>90.13</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>101.9995</t>
+          <t>95.648</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>0.3493</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>0.2134</t>
+          <t>0.0772</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.3379</t>
+          <t>0.2907</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>74.78</t>
+          <t>64.04</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>46.92</t>
+          <t>32.46</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>19.76</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.1881</t>
+          <t>0.1141</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>40.69</t>
+          <t>44.12</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>89.21</t>
+          <t>91.39</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.5154</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>0.1289</t>
+          <t>0.2341</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr"/>
@@ -10563,47 +10535,47 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>681546</t>
+          <t>670042</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>James Outman</t>
+          <t>Luke Raley</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-19T02:07:00Z</t>
+          <t>2026-07-19T00:08:00Z</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>Logan Webb</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>680570</t>
+          <t>657277</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -10612,7 +10584,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>46.6</v>
+        <v>46.7</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -10626,65 +10598,61 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>27.7</v>
+        <v>54.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>60.5</v>
+        <v>31.2</v>
       </c>
       <c r="R37" t="n">
-        <v>67.2</v>
+        <v>38.4</v>
       </c>
       <c r="S37" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T37" t="n">
         <v>80</v>
       </c>
       <c r="U37" t="n">
-        <v>0.8</v>
+        <v>19.5</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr"/>
@@ -10701,12 +10669,12 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -10716,12 +10684,12 @@
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 9.8 HR allowed</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -10731,112 +10699,112 @@
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>14.73</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>33.73</t>
+          <t>45.03</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>86.95</t>
+          <t>90.13</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>98.0212</t>
+          <t>101.9995</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>0.2838</t>
+          <t>0.456</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>0.1335</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>0.2272</t>
+          <t>0.3379</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>72.25</t>
+          <t>74.78</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>50.48</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>52.59</t>
+          <t>46.92</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.1513</t>
+          <t>0.1881</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>40.69</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>89.21</t>
         </is>
       </c>
       <c r="BD37" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.1289</t>
         </is>
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BG37" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI37" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ37" t="inlineStr"/>
@@ -11152,7 +11120,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -12016,7 +11984,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>43.6</v>
+        <v>44.2</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -12030,7 +11998,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -12043,7 +12011,7 @@
         <v>67.2</v>
       </c>
       <c r="S42" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T42" t="n">
         <v>80</v>
@@ -12053,39 +12021,35 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -12836,7 +12800,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -13116,7 +13080,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -13396,7 +13360,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -13676,7 +13640,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -14236,7 +14200,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -14796,7 +14760,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -15356,7 +15320,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -15636,7 +15600,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -17106,7 +17070,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>65.09999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -17120,7 +17084,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -17133,7 +17097,7 @@
         <v>67.2</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -17143,39 +17107,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -17646,7 +17606,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -18230,7 +18190,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>59.4</v>
+        <v>60</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -18244,7 +18204,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -18257,7 +18217,7 @@
         <v>67.2</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
@@ -18267,39 +18227,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -18465,27 +18421,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>671277</t>
+          <t>693307</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Luis García Jr.</t>
+          <t>Dillon Dingler</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-19T02:05:00Z</t>
+          <t>2026-07-19T02:07:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -18500,12 +18456,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>J.T. Ginn</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>669372</t>
+          <t>680570</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -18514,7 +18470,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>59.3</v>
+        <v>59.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -18528,26 +18484,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>48.7</v>
+        <v>49.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>33.3</v>
+        <v>60.5</v>
       </c>
       <c r="R10" t="n">
-        <v>71.40000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="S10" t="n">
         <v>100</v>
       </c>
       <c r="T10" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>66.90000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -18582,7 +18538,7 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -18599,27 +18555,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/23, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 14.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -18629,112 +18585,112 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.81</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>46.57</t>
+          <t>46.33</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>91.39</t>
+          <t>89.79</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.8855</t>
+          <t>101.1126</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4987</t>
+          <t>0.5072</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.2072</t>
+          <t>0.2193</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3537</t>
+          <t>0.3685</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>73.24</t>
+          <t>71.91</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>34.44</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.66</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>0.2149</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>37.57</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>87.56</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.3775</t>
+          <t>0.531</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1428</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr"/>
@@ -18745,12 +18701,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>693307</t>
+          <t>690993</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dillon Dingler</t>
+          <t>Colt Keith</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -18775,7 +18731,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -18794,7 +18750,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>59.1</v>
+        <v>59.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -18808,11 +18764,11 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>49.3</v>
+        <v>37.5</v>
       </c>
       <c r="Q11" t="n">
         <v>60.5</v>
@@ -18821,49 +18777,45 @@
         <v>67.2</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>8.1</v>
+        <v>38.7</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -18883,27 +18835,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/23, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -18913,67 +18865,67 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>8.36</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>42.72</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.79</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>101.1126</t>
+          <t>100.2207</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.5072</t>
+          <t>0.4342</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.2193</t>
+          <t>0.1716</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3685</t>
+          <t>0.3284</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>71.91</t>
+          <t>71.61</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>40.66</t>
+          <t>38.78</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.2149</t>
+          <t>0.1493</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -19029,27 +18981,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>690993</t>
+          <t>671277</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Colt Keith</t>
+          <t>Luis García Jr.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-19T02:07:00Z</t>
+          <t>2026-07-19T02:05:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -19059,17 +19011,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>J.T. Ginn</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>680570</t>
+          <t>669372</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -19078,7 +19030,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>59</v>
+        <v>59.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -19092,65 +19044,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>37.5</v>
+        <v>48.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>60.5</v>
+        <v>33.3</v>
       </c>
       <c r="R12" t="n">
-        <v>67.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>38.7</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -19167,19 +19115,19 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AK12" t="inlineStr">
         <is>
           <t>Hot streak: 2 HR in last 7 games</t>
@@ -19187,7 +19135,7 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 14.2 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -19197,112 +19145,112 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>42.72</t>
+          <t>46.57</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>91.39</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100.2207</t>
+          <t>101.8855</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4342</t>
+          <t>0.4987</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1716</t>
+          <t>0.2072</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3284</t>
+          <t>0.3537</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>71.61</t>
+          <t>73.24</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>34.44</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>38.78</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1493</t>
+          <t>0.237</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>37.57</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>87.56</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>0.3775</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.1428</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr"/>
@@ -19362,7 +19310,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>58.7</v>
+        <v>59.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -19376,7 +19324,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -19389,7 +19337,7 @@
         <v>67.2</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
@@ -19399,39 +19347,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -19597,27 +19541,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>646240</t>
+          <t>805808</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rafael Devers</t>
+          <t>Kevin McGonigle</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-19T00:08:00Z</t>
+          <t>2026-07-19T02:07:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -19627,17 +19571,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>680570</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -19646,7 +19590,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>57.4</v>
+        <v>57.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -19660,26 +19604,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>58.7</v>
+        <v>34.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.4</v>
+        <v>60.5</v>
       </c>
       <c r="R14" t="n">
-        <v>38.4</v>
+        <v>67.2</v>
       </c>
       <c r="S14" t="n">
-        <v>94.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T14" t="n">
         <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>36.3</v>
+        <v>33.7</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -19693,7 +19637,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -19714,7 +19658,7 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -19736,7 +19680,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -19746,127 +19690,127 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Last 7 games: 6/27, 1 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 14.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>51.97</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>103.1178</t>
+          <t>98.4601</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.4653</t>
+          <t>0.441</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.2301</t>
+          <t>0.173</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3376</t>
+          <t>0.363</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>71.74</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>42.71</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>89.45</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3835</t>
+          <t>0.531</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1513</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>29.11</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -19877,24 +19821,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>686527</t>
+          <t>646240</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dominic Canzone</t>
+          <t>Rafael Devers</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-07-19T00:08:00Z</t>
@@ -19902,22 +19846,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Logan Webb</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>657277</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -19926,7 +19870,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -19944,22 +19888,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>62.8</v>
+        <v>58.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>31.2</v>
+        <v>41.4</v>
       </c>
       <c r="R15" t="n">
         <v>38.4</v>
       </c>
       <c r="S15" t="n">
-        <v>96.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T15" t="n">
         <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>49.7</v>
+        <v>36.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -19973,7 +19917,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -20016,22 +19960,22 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 9.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 14.8 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -20041,97 +19985,97 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>12.92</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>51.97</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>92.58</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>103.1752</t>
+          <t>103.1178</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.5218</t>
+          <t>0.4653</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.2437</t>
+          <t>0.2301</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3718</t>
+          <t>0.3376</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>74.29</t>
+          <t>71.74</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>44.61</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>0.227</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>40.69</t>
+          <t>42.71</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>89.21</t>
+          <t>89.45</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3835</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1289</t>
+          <t>0.1513</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>29.11</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
@@ -20157,47 +20101,47 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>805808</t>
+          <t>686527</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kevin McGonigle</t>
+          <t>Dominic Canzone</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-19T02:07:00Z</t>
+          <t>2026-07-19T00:08:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>Logan Webb</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>680570</t>
+          <t>657277</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -20206,7 +20150,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>57.1</v>
+        <v>57.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -20220,65 +20164,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>34.1</v>
+        <v>62.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>60.5</v>
+        <v>31.2</v>
       </c>
       <c r="R16" t="n">
-        <v>67.2</v>
+        <v>38.4</v>
       </c>
       <c r="S16" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T16" t="n">
         <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>33.7</v>
+        <v>49.7</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -20300,137 +20240,137 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 9.8 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>48.51</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>92.58</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>98.4601</t>
+          <t>103.1752</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.441</t>
+          <t>0.5218</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.2437</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>0.3718</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>74.29</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>44.61</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.237</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>40.69</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>89.21</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.1289</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr"/>
@@ -21586,7 +21526,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
